--- a/material_comparison_tool/output/comparison/Anhui Province_radiative_cooling_comparison.xlsx
+++ b/material_comparison_tool/output/comparison/Anhui Province_radiative_cooling_comparison.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,25 +506,60 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Daily_HVAC_kWh_per_m2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Floor_Area_m2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Peak_Cooling_Load_kW</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Peak_Heating_Load_kW</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Simulation_Days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Sampling_Scale</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Hours</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Cooling_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_Heating_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Raw_Total_HVAC_Energy_kWh</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Delta_Energy_kWh</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Saving_%</t>
         </is>
@@ -538,12 +573,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>基准</t>
+          <t>对比基准</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>默认材料参数，用作对比基线</t>
+          <t>默认建筑材料（墙α≈0.6, ε≈0.9；屋面α≈0.7, ε≈0.9）</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -565,36 +600,57 @@
         <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4768.362626710604</v>
+        <v>1591.768477733835</v>
       </c>
       <c r="K2" t="n">
-        <v>6163.00043758916</v>
+        <v>2113.237620916204</v>
       </c>
       <c r="L2" t="n">
-        <v>10931.36306429976</v>
+        <v>3705.006098650038</v>
       </c>
       <c r="M2" t="n">
-        <v>171.6610545615817</v>
+        <v>57.30366519841805</v>
       </c>
       <c r="N2" t="n">
-        <v>221.8680157532098</v>
+        <v>76.07655435298334</v>
       </c>
       <c r="O2" t="n">
-        <v>393.5290703147915</v>
+        <v>133.3802195514014</v>
       </c>
       <c r="P2" t="n">
+        <v>0.3070447043080142</v>
+      </c>
+      <c r="Q2" t="n">
         <v>100</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.215623645959379</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.945116682035099</v>
+        <v>3.212911238603903</v>
       </c>
       <c r="S2" t="n">
+        <v>1.933188099016875</v>
+      </c>
+      <c r="T2" t="n">
+        <v>120.6666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2896</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1591.768477733835</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2113.237620916204</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3705.006098650038</v>
+      </c>
+      <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AA2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -606,12 +662,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>（高反射+高发射）</t>
+          <t>辐射制冷</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>α=0.1, ε=0.95（辐射制冷友好）；</t>
+          <t>高反射、高发射率材料（如 α=0.1, ε=0.95）</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -633,37 +689,58 @@
         <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2430.722273146543</v>
+        <v>815.2616159759997</v>
       </c>
       <c r="K3" t="n">
-        <v>7106.279508707739</v>
+        <v>2429.845627547386</v>
       </c>
       <c r="L3" t="n">
-        <v>9537.001781854282</v>
+        <v>3245.107243523386</v>
       </c>
       <c r="M3" t="n">
-        <v>87.50600183327553</v>
+        <v>29.34941817513599</v>
       </c>
       <c r="N3" t="n">
-        <v>255.8260623134786</v>
+        <v>87.47444259170592</v>
       </c>
       <c r="O3" t="n">
-        <v>343.3320641467541</v>
+        <v>116.8238607668419</v>
       </c>
       <c r="P3" t="n">
+        <v>0.2689315395185126</v>
+      </c>
+      <c r="Q3" t="n">
         <v>100</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1.39051195995594</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.948211010693769</v>
-      </c>
       <c r="S3" t="n">
-        <v>-1394.361282445481</v>
+        <v>1.936281588186372</v>
       </c>
       <c r="T3" t="n">
-        <v>12.75560306837911</v>
+        <v>120.6666666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2896</v>
+      </c>
+      <c r="W3" t="n">
+        <v>815.2616159759997</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2429.845627547386</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3245.107243523386</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-459.8988551266525</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.41290413244453</v>
       </c>
     </row>
     <row r="4">
@@ -674,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>（高吸收+高发射）</t>
+          <t>辐射制热/保温</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>α=0.9, ε=0.95（辐射制热）；墙体不变</t>
+          <t>高吸收、高发射率材料（如 α=0.9, ε=0.95）</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -701,37 +778,58 @@
         <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>6118.070336349483</v>
+        <v>2042.981794359554</v>
       </c>
       <c r="K4" t="n">
-        <v>5947.283293802805</v>
+        <v>2042.300945557807</v>
       </c>
       <c r="L4" t="n">
-        <v>12065.35363015229</v>
+        <v>4085.28273991736</v>
       </c>
       <c r="M4" t="n">
-        <v>220.2505321085814</v>
+        <v>73.54734459694393</v>
       </c>
       <c r="N4" t="n">
-        <v>214.102198576901</v>
+        <v>73.52283404008104</v>
       </c>
       <c r="O4" t="n">
-        <v>434.3527306854824</v>
+        <v>147.070178637025</v>
       </c>
       <c r="P4" t="n">
+        <v>0.338559343087074</v>
+      </c>
+      <c r="Q4" t="n">
         <v>100</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.303548143522514</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.948211010693769</v>
+        <v>3.288715807763973</v>
       </c>
       <c r="S4" t="n">
-        <v>1133.990565852524</v>
+        <v>1.936281588186372</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.37373435666017</v>
+        <v>120.6666666666667</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>2896</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2042.981794359554</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2042.300945557807</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4085.28273991736</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>380.2766412673218</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-10.26386006235941</v>
       </c>
     </row>
   </sheetData>
